--- a/ridimensionamento foto.xlsx
+++ b/ridimensionamento foto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enrico\Documents\git-hub\sitokkd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CA23A8-AEF2-4485-83F1-185BD8918273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D548B9F-FFAF-4741-87B2-5EF67592CF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="0" windowWidth="23256" windowHeight="11736" xr2:uid="{A17BD42F-DCE5-4F61-B23C-941DFB35D489}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="11736" xr2:uid="{A17BD42F-DCE5-4F61-B23C-941DFB35D489}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -489,13 +489,13 @@
         <v>0</v>
       </c>
       <c r="B4" s="5">
-        <v>5996</v>
+        <v>1224</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="5">
-        <v>4002</v>
+        <v>816</v>
       </c>
       <c r="G4" s="2"/>
     </row>
@@ -508,14 +508,14 @@
       </c>
       <c r="B6" s="3">
         <f>+B4</f>
-        <v>5996</v>
+        <v>1224</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="4">
         <f>+B6/G1</f>
-        <v>3372.75</v>
+        <v>688.5</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
@@ -527,14 +527,14 @@
       </c>
       <c r="B8" s="4">
         <f>+D8*G1</f>
-        <v>7114.6666666666661</v>
+        <v>1450.6666666666665</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="4">
         <f>+D4</f>
-        <v>4002</v>
+        <v>816</v>
       </c>
       <c r="Q8" s="1">
         <v>475</v>
@@ -562,11 +562,11 @@
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <f>+B4/B1</f>
-        <v>3.1229166666666668</v>
+        <v>0.63749999999999996</v>
       </c>
       <c r="D10" s="1">
         <f>+D4/D1</f>
-        <v>3.7055555555555557</v>
+        <v>0.75555555555555554</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
@@ -575,24 +575,24 @@
       </c>
       <c r="B12" s="3">
         <f>+B4/B10</f>
-        <v>1920</v>
+        <v>1920.0000000000002</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="4">
         <f>+D4/B10</f>
-        <v>1281.4943295530354</v>
+        <v>1280</v>
       </c>
       <c r="H12">
         <f>+B12-B4</f>
-        <v>-4076</v>
+        <v>696.00000000000023</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="H13">
         <f>+H12/2</f>
-        <v>-2038</v>
+        <v>348.00000000000011</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
@@ -601,7 +601,7 @@
       </c>
       <c r="B14" s="4">
         <f>+B4/D10</f>
-        <v>1618.1109445277361</v>
+        <v>1620</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>1</v>
